--- a/Results_experiment/exp_5/preds_1111112222222222.xlsx
+++ b/Results_experiment/exp_5/preds_1111112222222222.xlsx
@@ -1596,7 +1596,7 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>2.360338926315308</v>
+        <v>1.84041166305542</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1610,7 +1610,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D3">
-        <v>2.273234128952026</v>
+        <v>1.925944566726685</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1624,7 +1624,7 @@
         <v>21.89999961853027</v>
       </c>
       <c r="D4">
-        <v>16.50183486938477</v>
+        <v>16.46552658081055</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1638,7 +1638,7 @@
         <v>25.89999961853027</v>
       </c>
       <c r="D5">
-        <v>14.4255428314209</v>
+        <v>15.83079814910889</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1652,7 +1652,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D6">
-        <v>2.478431701660156</v>
+        <v>2.584781885147095</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1666,7 +1666,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D7">
-        <v>4.528110027313232</v>
+        <v>4.870302200317383</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1680,7 +1680,7 @@
         <v>27.39999961853027</v>
       </c>
       <c r="D8">
-        <v>19.7764892578125</v>
+        <v>19.65681076049805</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1694,7 +1694,7 @@
         <v>20.5</v>
       </c>
       <c r="D9">
-        <v>10.00469970703125</v>
+        <v>10.65840911865234</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1708,7 +1708,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D10">
-        <v>6.444785118103027</v>
+        <v>6.397379875183105</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1722,7 +1722,7 @@
         <v>33.09999847412109</v>
       </c>
       <c r="D11">
-        <v>24.18841934204102</v>
+        <v>21.17296981811523</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1736,7 +1736,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D12">
-        <v>4.274466991424561</v>
+        <v>4.699278831481934</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1750,7 +1750,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D13">
-        <v>2.750246047973633</v>
+        <v>3.062610864639282</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1764,7 +1764,7 @@
         <v>4</v>
       </c>
       <c r="D14">
-        <v>2.836591243743896</v>
+        <v>4.240859985351562</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1778,7 +1778,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D15">
-        <v>2.445517778396606</v>
+        <v>3.822851181030273</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1792,7 +1792,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D16">
-        <v>3.326486349105835</v>
+        <v>4.286641120910645</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1806,7 +1806,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D17">
-        <v>1.850782871246338</v>
+        <v>2.641830682754517</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1820,7 +1820,7 @@
         <v>12</v>
       </c>
       <c r="D18">
-        <v>7.47459602355957</v>
+        <v>11.15294551849365</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1834,7 +1834,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>1.91807746887207</v>
+        <v>2.000091075897217</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1848,7 +1848,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D20">
-        <v>1.396326184272766</v>
+        <v>1.408353328704834</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1862,7 +1862,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D21">
-        <v>5.384835243225098</v>
+        <v>5.036250114440918</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1876,7 +1876,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D22">
-        <v>1.381244659423828</v>
+        <v>1.317883610725403</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1890,7 +1890,7 @@
         <v>13.80000019073486</v>
       </c>
       <c r="D23">
-        <v>9.783210754394531</v>
+        <v>9.791836738586426</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1904,7 +1904,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D24">
-        <v>1.387250065803528</v>
+        <v>1.328034162521362</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1918,7 +1918,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D25">
-        <v>2.523905515670776</v>
+        <v>1.723318696022034</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1932,7 +1932,7 @@
         <v>37.90000152587891</v>
       </c>
       <c r="D26">
-        <v>29.76092147827148</v>
+        <v>30.86419105529785</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1946,7 +1946,7 @@
         <v>5.5</v>
       </c>
       <c r="D27">
-        <v>5.497159004211426</v>
+        <v>5.251697540283203</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1960,7 +1960,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D28">
-        <v>5.818753242492676</v>
+        <v>5.846131324768066</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1974,7 +1974,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D29">
-        <v>3.09196949005127</v>
+        <v>3.380208015441895</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1988,7 +1988,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D30">
-        <v>1.468499541282654</v>
+        <v>2.063258647918701</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2002,7 +2002,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D31">
-        <v>2.015330791473389</v>
+        <v>2.598287105560303</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2016,7 +2016,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D32">
-        <v>1.385059595108032</v>
+        <v>2.660439014434814</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2030,7 +2030,7 @@
         <v>5.5</v>
       </c>
       <c r="D33">
-        <v>3.212451934814453</v>
+        <v>5.498867034912109</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2044,7 +2044,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D34">
-        <v>2.454333305358887</v>
+        <v>2.943341493606567</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2058,7 +2058,7 @@
         <v>4.5</v>
       </c>
       <c r="D35">
-        <v>6.203932762145996</v>
+        <v>5.470821380615234</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2072,7 +2072,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D36">
-        <v>2.022583961486816</v>
+        <v>2.720643520355225</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2086,7 +2086,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D37">
-        <v>2.707156181335449</v>
+        <v>1.710292339324951</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2100,7 +2100,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D38">
-        <v>1.405217885971069</v>
+        <v>1.978750467300415</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2114,7 +2114,7 @@
         <v>0.5</v>
       </c>
       <c r="D39">
-        <v>1.431077837944031</v>
+        <v>1.357937932014465</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2128,7 +2128,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D40">
-        <v>2.122113466262817</v>
+        <v>2.556208372116089</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2142,7 +2142,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D41">
-        <v>1.379326105117798</v>
+        <v>1.322992324829102</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2156,7 +2156,7 @@
         <v>10.10000038146973</v>
       </c>
       <c r="D42">
-        <v>5.086660861968994</v>
+        <v>4.951504707336426</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2170,7 +2170,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D43">
-        <v>1.376943945884705</v>
+        <v>1.738157153129578</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2184,7 +2184,7 @@
         <v>5</v>
       </c>
       <c r="D44">
-        <v>3.564555883407593</v>
+        <v>3.552829504013062</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2198,7 +2198,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D45">
-        <v>2.149746894836426</v>
+        <v>2.282649040222168</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2212,7 +2212,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D46">
-        <v>3.338982343673706</v>
+        <v>4.902947425842285</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2226,7 +2226,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D47">
-        <v>1.439470052719116</v>
+        <v>2.973023414611816</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2240,7 +2240,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D48">
-        <v>5.113416194915771</v>
+        <v>4.613939762115479</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2254,7 +2254,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D49">
-        <v>1.43827486038208</v>
+        <v>1.7756427526474</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2268,7 +2268,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D50">
-        <v>5.713077545166016</v>
+        <v>7.299544334411621</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2282,7 +2282,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D51">
-        <v>2.01584267616272</v>
+        <v>2.665585041046143</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2296,7 +2296,7 @@
         <v>1</v>
       </c>
       <c r="D52">
-        <v>2.697167873382568</v>
+        <v>3.112827301025391</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2310,7 +2310,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D53">
-        <v>1.845811605453491</v>
+        <v>2.935300350189209</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2324,7 +2324,7 @@
         <v>5.5</v>
       </c>
       <c r="D54">
-        <v>2.358798503875732</v>
+        <v>3.374640703201294</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2338,7 +2338,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D55">
-        <v>1.366794347763062</v>
+        <v>1.32116961479187</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2352,7 +2352,7 @@
         <v>34</v>
       </c>
       <c r="D56">
-        <v>21.29009819030762</v>
+        <v>21.14043235778809</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2366,7 +2366,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D57">
-        <v>4.18431568145752</v>
+        <v>3.552669048309326</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2380,7 +2380,7 @@
         <v>1</v>
       </c>
       <c r="D58">
-        <v>1.644991636276245</v>
+        <v>1.827286958694458</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2394,7 +2394,7 @@
         <v>3.5</v>
       </c>
       <c r="D59">
-        <v>1.990917444229126</v>
+        <v>2.620322227478027</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2408,7 +2408,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D60">
-        <v>3.083429336547852</v>
+        <v>3.194011926651001</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2422,7 +2422,7 @@
         <v>6</v>
       </c>
       <c r="D61">
-        <v>1.394469976425171</v>
+        <v>1.904792070388794</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2436,7 +2436,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D62">
-        <v>4.967365264892578</v>
+        <v>4.888554573059082</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2450,7 +2450,7 @@
         <v>8</v>
       </c>
       <c r="D63">
-        <v>8.221677780151367</v>
+        <v>7.794179916381836</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2464,7 +2464,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D64">
-        <v>1.717299938201904</v>
+        <v>1.806734204292297</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2478,7 +2478,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D65">
-        <v>10.42705154418945</v>
+        <v>9.766205787658691</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2492,7 +2492,7 @@
         <v>28.20000076293945</v>
       </c>
       <c r="D66">
-        <v>16.2866268157959</v>
+        <v>16.08058166503906</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2506,7 +2506,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D67">
-        <v>5.392973899841309</v>
+        <v>5.510195732116699</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2520,7 +2520,7 @@
         <v>0.5</v>
       </c>
       <c r="D68">
-        <v>1.406740427017212</v>
+        <v>2.041889667510986</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2534,7 +2534,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D69">
-        <v>7.987785339355469</v>
+        <v>8.501119613647461</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2548,7 +2548,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D70">
-        <v>2.323463916778564</v>
+        <v>2.086087942123413</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2562,7 +2562,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D71">
-        <v>1.369043469429016</v>
+        <v>1.526499271392822</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2576,7 +2576,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D72">
-        <v>3.435932874679565</v>
+        <v>3.833903312683105</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2590,7 +2590,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D73">
-        <v>1.950830817222595</v>
+        <v>1.839929103851318</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2604,7 +2604,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D74">
-        <v>5.914360046386719</v>
+        <v>7.523909568786621</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2618,7 +2618,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D75">
-        <v>4.671058654785156</v>
+        <v>3.170327663421631</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>1.986696839332581</v>
+        <v>1.831480503082275</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2646,7 +2646,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D77">
-        <v>2.149100303649902</v>
+        <v>1.844473123550415</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2660,7 +2660,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D78">
-        <v>6.000362396240234</v>
+        <v>5.305733680725098</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2674,7 +2674,7 @@
         <v>9.5</v>
       </c>
       <c r="D79">
-        <v>6.193324089050293</v>
+        <v>5.311086654663086</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2688,7 +2688,7 @@
         <v>0.5</v>
       </c>
       <c r="D80">
-        <v>2.502569675445557</v>
+        <v>2.131844043731689</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2702,7 +2702,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D81">
-        <v>3.475484371185303</v>
+        <v>2.424060106277466</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2716,7 +2716,7 @@
         <v>1.5</v>
       </c>
       <c r="D82">
-        <v>2.509602308273315</v>
+        <v>1.791906356811523</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2730,7 +2730,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D83">
-        <v>1.549973249435425</v>
+        <v>1.719819188117981</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2744,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="D84">
-        <v>3.008588314056396</v>
+        <v>3.759250402450562</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2758,7 +2758,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D85">
-        <v>2.636082172393799</v>
+        <v>2.544991731643677</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2772,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="D86">
-        <v>1.532583594322205</v>
+        <v>1.672163605690002</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2786,7 +2786,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D87">
-        <v>8.000167846679688</v>
+        <v>7.577800750732422</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2800,7 +2800,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D88">
-        <v>2.522090673446655</v>
+        <v>2.254539966583252</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2814,7 +2814,7 @@
         <v>15</v>
       </c>
       <c r="D89">
-        <v>12.98465538024902</v>
+        <v>13.07785511016846</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2828,7 +2828,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D90">
-        <v>5.964771270751953</v>
+        <v>7.11430549621582</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2842,7 +2842,7 @@
         <v>14</v>
       </c>
       <c r="D91">
-        <v>8.342921257019043</v>
+        <v>9.251439094543457</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2856,7 +2856,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D92">
-        <v>2.93189811706543</v>
+        <v>1.559503078460693</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2870,7 +2870,7 @@
         <v>7.5</v>
       </c>
       <c r="D93">
-        <v>2.744986295700073</v>
+        <v>3.982767343521118</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2884,7 +2884,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D94">
-        <v>1.375540256500244</v>
+        <v>1.432558178901672</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2898,7 +2898,7 @@
         <v>2</v>
       </c>
       <c r="D95">
-        <v>2.440083265304565</v>
+        <v>3.426291704177856</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2912,7 +2912,7 @@
         <v>15.5</v>
       </c>
       <c r="D96">
-        <v>10.20039081573486</v>
+        <v>9.591418266296387</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2926,7 +2926,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D97">
-        <v>2.513992786407471</v>
+        <v>3.121303081512451</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2940,7 +2940,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D98">
-        <v>20.48812103271484</v>
+        <v>18.35575485229492</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2954,7 +2954,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D99">
-        <v>3.527458429336548</v>
+        <v>2.803834915161133</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2968,7 +2968,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D100">
-        <v>2.557025671005249</v>
+        <v>1.781063079833984</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2982,7 +2982,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D101">
-        <v>1.990013837814331</v>
+        <v>2.605438709259033</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2996,7 +2996,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D102">
-        <v>1.410338878631592</v>
+        <v>1.892127275466919</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3010,7 +3010,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D103">
-        <v>6.325052261352539</v>
+        <v>3.95445704460144</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3024,7 +3024,7 @@
         <v>2</v>
       </c>
       <c r="D104">
-        <v>3.802542924880981</v>
+        <v>2.569239854812622</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3038,7 +3038,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D105">
-        <v>5.613937377929688</v>
+        <v>5.944365501403809</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3052,7 +3052,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D106">
-        <v>2.551328182220459</v>
+        <v>2.650407314300537</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3066,7 +3066,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D107">
-        <v>1.975297808647156</v>
+        <v>2.509122371673584</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3080,7 +3080,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D108">
-        <v>5.459006309509277</v>
+        <v>5.80854320526123</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3094,7 +3094,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D109">
-        <v>2.412266731262207</v>
+        <v>2.619074821472168</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3108,7 +3108,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D110">
-        <v>1.597585320472717</v>
+        <v>1.744953632354736</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3122,7 +3122,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D111">
-        <v>2.558301448822021</v>
+        <v>2.576848983764648</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3136,7 +3136,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D112">
-        <v>5.236908912658691</v>
+        <v>6.970010757446289</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3150,7 +3150,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D113">
-        <v>2.872747182846069</v>
+        <v>2.059619188308716</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3164,7 +3164,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D114">
-        <v>4.433285713195801</v>
+        <v>5.17424201965332</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3178,7 +3178,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D115">
-        <v>2.465776443481445</v>
+        <v>2.060327291488647</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3192,7 +3192,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D116">
-        <v>4.660592079162598</v>
+        <v>6.132929801940918</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3206,7 +3206,7 @@
         <v>2</v>
       </c>
       <c r="D117">
-        <v>3.155204296112061</v>
+        <v>3.268904447555542</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3220,7 +3220,7 @@
         <v>2</v>
       </c>
       <c r="D118">
-        <v>2.191920518875122</v>
+        <v>1.81780481338501</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3234,7 +3234,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D119">
-        <v>1.914751768112183</v>
+        <v>2.064574480056763</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3248,7 +3248,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D120">
-        <v>9.459177017211914</v>
+        <v>9.822140693664551</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3262,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="D121">
-        <v>1.877799510955811</v>
+        <v>1.869039416313171</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3276,7 +3276,7 @@
         <v>31.39999961853027</v>
       </c>
       <c r="D122">
-        <v>20.97317314147949</v>
+        <v>21.27675247192383</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3290,7 +3290,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D123">
-        <v>2.91788649559021</v>
+        <v>2.801007032394409</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3304,7 +3304,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D124">
-        <v>2.392092943191528</v>
+        <v>2.83475399017334</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3318,7 +3318,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D125">
-        <v>1.519028902053833</v>
+        <v>1.899096012115479</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3332,7 +3332,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D126">
-        <v>2.261548042297363</v>
+        <v>1.888236522674561</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3346,7 +3346,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D127">
-        <v>5.392411231994629</v>
+        <v>5.721830368041992</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3360,7 +3360,7 @@
         <v>2</v>
       </c>
       <c r="D128">
-        <v>2.309130191802979</v>
+        <v>2.77829384803772</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3374,7 +3374,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D129">
-        <v>2.286133289337158</v>
+        <v>2.07679295539856</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3388,7 +3388,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D130">
-        <v>2.774019479751587</v>
+        <v>3.444148778915405</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3402,7 +3402,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D131">
-        <v>2.81452751159668</v>
+        <v>2.943708419799805</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3416,7 +3416,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D132">
-        <v>3.929386854171753</v>
+        <v>4.319253921508789</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3430,7 +3430,7 @@
         <v>1.5</v>
       </c>
       <c r="D133">
-        <v>1.515637397766113</v>
+        <v>1.864196538925171</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3444,7 +3444,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D134">
-        <v>2.632027864456177</v>
+        <v>3.093161106109619</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3458,7 +3458,7 @@
         <v>3.5</v>
       </c>
       <c r="D135">
-        <v>1.842545747756958</v>
+        <v>2.008221626281738</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3472,7 +3472,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D136">
-        <v>2.923705339431763</v>
+        <v>2.451994180679321</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3486,7 +3486,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D137">
-        <v>6.384742736816406</v>
+        <v>6.928260803222656</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3500,7 +3500,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D138">
-        <v>1.414289593696594</v>
+        <v>1.874514222145081</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3514,7 +3514,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D139">
-        <v>1.3925461769104</v>
+        <v>1.337476253509521</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3528,7 +3528,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D140">
-        <v>2.909318447113037</v>
+        <v>3.682034730911255</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3542,7 +3542,7 @@
         <v>6</v>
       </c>
       <c r="D141">
-        <v>6.896074295043945</v>
+        <v>7.570023536682129</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3556,7 +3556,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D142">
-        <v>1.568397402763367</v>
+        <v>2.09722900390625</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3570,7 +3570,7 @@
         <v>4</v>
       </c>
       <c r="D143">
-        <v>3.853360891342163</v>
+        <v>5.635119438171387</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3584,7 +3584,7 @@
         <v>3</v>
       </c>
       <c r="D144">
-        <v>2.671221971511841</v>
+        <v>1.693290114402771</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3598,7 +3598,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D145">
-        <v>7.434310913085938</v>
+        <v>8.596590995788574</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3612,7 +3612,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D146">
-        <v>1.904794216156006</v>
+        <v>1.717321515083313</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3626,7 +3626,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D147">
-        <v>1.42741584777832</v>
+        <v>1.853731155395508</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3640,7 +3640,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D148">
-        <v>1.930155754089355</v>
+        <v>2.939192771911621</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3654,7 +3654,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D149">
-        <v>6.508750915527344</v>
+        <v>7.011116981506348</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3668,7 +3668,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D150">
-        <v>1.372201442718506</v>
+        <v>1.339898943901062</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3682,7 +3682,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D151">
-        <v>7.036005020141602</v>
+        <v>8.32364559173584</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3696,7 +3696,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D152">
-        <v>2.083891153335571</v>
+        <v>1.578731775283813</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3710,7 +3710,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D153">
-        <v>7.507508277893066</v>
+        <v>7.963129997253418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3724,7 +3724,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D154">
-        <v>1.470673799514771</v>
+        <v>1.316261529922485</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3738,7 +3738,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D155">
-        <v>1.393864154815674</v>
+        <v>1.344413876533508</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3752,7 +3752,7 @@
         <v>8</v>
       </c>
       <c r="D156">
-        <v>2.613434076309204</v>
+        <v>2.487761974334717</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3766,7 +3766,7 @@
         <v>12.30000019073486</v>
       </c>
       <c r="D157">
-        <v>6.329638481140137</v>
+        <v>7.421709060668945</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3780,7 +3780,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D158">
-        <v>1.565430283546448</v>
+        <v>1.750080347061157</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3794,7 +3794,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D159">
-        <v>3.469331026077271</v>
+        <v>1.843753695487976</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3808,7 +3808,7 @@
         <v>9</v>
       </c>
       <c r="D160">
-        <v>2.825841426849365</v>
+        <v>2.483945369720459</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3822,7 +3822,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D161">
-        <v>1.75664234161377</v>
+        <v>1.842235207557678</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3836,7 +3836,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D162">
-        <v>1.405616998672485</v>
+        <v>1.524320125579834</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3850,7 +3850,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D163">
-        <v>4.869127750396729</v>
+        <v>4.795445442199707</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3864,7 +3864,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D164">
-        <v>2.740564823150635</v>
+        <v>2.137195110321045</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3878,7 +3878,7 @@
         <v>2</v>
       </c>
       <c r="D165">
-        <v>3.432451963424683</v>
+        <v>3.293744802474976</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3892,7 +3892,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D166">
-        <v>3.507762432098389</v>
+        <v>4.674464225769043</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3906,7 +3906,7 @@
         <v>4.5</v>
       </c>
       <c r="D167">
-        <v>1.573367595672607</v>
+        <v>2.157332420349121</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3920,7 +3920,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D168">
-        <v>1.581655263900757</v>
+        <v>2.409588098526001</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3934,7 +3934,7 @@
         <v>3.5</v>
       </c>
       <c r="D169">
-        <v>1.370100140571594</v>
+        <v>1.659320831298828</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3948,7 +3948,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D170">
-        <v>2.436686992645264</v>
+        <v>2.232822895050049</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3962,7 +3962,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D171">
-        <v>2.284953117370605</v>
+        <v>1.528719902038574</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3976,7 +3976,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D172">
-        <v>3.95631742477417</v>
+        <v>4.59172248840332</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3990,7 +3990,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D173">
-        <v>1.589831233024597</v>
+        <v>2.575788736343384</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4004,7 +4004,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D174">
-        <v>4.453768253326416</v>
+        <v>4.514310836791992</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4018,7 +4018,7 @@
         <v>2</v>
       </c>
       <c r="D175">
-        <v>2.225921154022217</v>
+        <v>2.000386238098145</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4032,7 +4032,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D176">
-        <v>3.242486715316772</v>
+        <v>3.242622137069702</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4046,7 +4046,7 @@
         <v>3</v>
       </c>
       <c r="D177">
-        <v>1.456019163131714</v>
+        <v>2.027621746063232</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4060,7 +4060,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D178">
-        <v>5.995095252990723</v>
+        <v>6.03266716003418</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4074,7 +4074,7 @@
         <v>28.39999961853027</v>
       </c>
       <c r="D179">
-        <v>14.45225715637207</v>
+        <v>14.53376579284668</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4088,7 +4088,7 @@
         <v>3</v>
       </c>
       <c r="D180">
-        <v>2.023231506347656</v>
+        <v>2.44682765007019</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4102,7 +4102,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D181">
-        <v>7.328619003295898</v>
+        <v>8.074268341064453</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4116,7 +4116,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D182">
-        <v>4.216270446777344</v>
+        <v>4.674552917480469</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4130,7 +4130,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D183">
-        <v>3.391996145248413</v>
+        <v>2.233026504516602</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4144,7 +4144,7 @@
         <v>8</v>
       </c>
       <c r="D184">
-        <v>6.275398254394531</v>
+        <v>7.387062072753906</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4158,7 +4158,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D185">
-        <v>1.447327852249146</v>
+        <v>1.380540251731873</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4172,7 +4172,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D186">
-        <v>3.559551477432251</v>
+        <v>4.878650665283203</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4186,7 +4186,7 @@
         <v>3</v>
       </c>
       <c r="D187">
-        <v>2.649750947952271</v>
+        <v>2.784511089324951</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4200,7 +4200,7 @@
         <v>4</v>
       </c>
       <c r="D188">
-        <v>1.708999276161194</v>
+        <v>3.60580039024353</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4214,7 +4214,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D189">
-        <v>1.803561925888062</v>
+        <v>1.796072721481323</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4228,7 +4228,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D190">
-        <v>2.594668388366699</v>
+        <v>2.169847249984741</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4242,7 +4242,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D191">
-        <v>1.372934341430664</v>
+        <v>1.414643049240112</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4256,7 +4256,7 @@
         <v>12.19999980926514</v>
       </c>
       <c r="D192">
-        <v>10.45027351379395</v>
+        <v>11.61640930175781</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4270,7 +4270,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D193">
-        <v>7.232302665710449</v>
+        <v>4.875338554382324</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4284,7 +4284,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D194">
-        <v>1.75248646736145</v>
+        <v>1.545793652534485</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4298,7 +4298,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D195">
-        <v>1.37537670135498</v>
+        <v>1.43124794960022</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4312,7 +4312,7 @@
         <v>17.39999961853027</v>
       </c>
       <c r="D196">
-        <v>13.55850791931152</v>
+        <v>13.34765720367432</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4326,7 +4326,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D197">
-        <v>4.546804904937744</v>
+        <v>4.780725955963135</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4340,7 +4340,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D198">
-        <v>1.381516218185425</v>
+        <v>1.301291346549988</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4354,7 +4354,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D199">
-        <v>5.599403381347656</v>
+        <v>6.137761116027832</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4368,7 +4368,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D200">
-        <v>1.554075241088867</v>
+        <v>1.715845108032227</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4382,7 +4382,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D201">
-        <v>1.429704666137695</v>
+        <v>1.815731763839722</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4396,7 +4396,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D202">
-        <v>1.889457106590271</v>
+        <v>1.852676868438721</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4410,7 +4410,7 @@
         <v>1.5</v>
       </c>
       <c r="D203">
-        <v>1.43635880947113</v>
+        <v>1.869621276855469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4424,7 +4424,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D204">
-        <v>4.620846748352051</v>
+        <v>3.877843141555786</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4438,7 +4438,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D205">
-        <v>1.370341181755066</v>
+        <v>1.626891732215881</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4452,7 +4452,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D206">
-        <v>10.3663330078125</v>
+        <v>10.56623363494873</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4466,7 +4466,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D207">
-        <v>2.346281290054321</v>
+        <v>2.447982311248779</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4480,7 +4480,7 @@
         <v>3.5</v>
       </c>
       <c r="D208">
-        <v>2.912215232849121</v>
+        <v>3.902750492095947</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4494,7 +4494,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D209">
-        <v>1.849821805953979</v>
+        <v>2.754655838012695</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4508,7 +4508,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D210">
-        <v>1.757450938224792</v>
+        <v>2.767480134963989</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4522,7 +4522,7 @@
         <v>3.5</v>
       </c>
       <c r="D211">
-        <v>2.99461555480957</v>
+        <v>2.797334909439087</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4536,7 +4536,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D212">
-        <v>2.977330923080444</v>
+        <v>2.324894666671753</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4550,7 +4550,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D213">
-        <v>3.838967084884644</v>
+        <v>3.537522077560425</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4564,7 +4564,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D214">
-        <v>2.613049030303955</v>
+        <v>2.430755376815796</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4578,7 +4578,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D215">
-        <v>2.152591705322266</v>
+        <v>2.131373882293701</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4592,7 +4592,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D216">
-        <v>1.731778860092163</v>
+        <v>2.090215444564819</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>2.37999439239502</v>
+        <v>2.750901222229004</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4620,7 +4620,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D218">
-        <v>1.690673112869263</v>
+        <v>1.884010672569275</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4634,7 +4634,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D219">
-        <v>2.765755414962769</v>
+        <v>2.719718217849731</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4648,7 +4648,7 @@
         <v>1.5</v>
       </c>
       <c r="D220">
-        <v>1.515527725219727</v>
+        <v>2.019550561904907</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4662,7 +4662,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D221">
-        <v>4.19635534286499</v>
+        <v>4.369441032409668</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4676,7 +4676,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D222">
-        <v>2.174319982528687</v>
+        <v>2.243144035339355</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4690,7 +4690,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D223">
-        <v>2.609135150909424</v>
+        <v>3.981191873550415</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4704,7 +4704,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D224">
-        <v>1.535776972770691</v>
+        <v>2.096988439559937</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4718,7 +4718,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D225">
-        <v>1.420324683189392</v>
+        <v>1.762198686599731</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4732,7 +4732,7 @@
         <v>2</v>
       </c>
       <c r="D226">
-        <v>3.222447395324707</v>
+        <v>3.959226846694946</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4746,7 +4746,7 @@
         <v>0.5</v>
       </c>
       <c r="D227">
-        <v>2.584530830383301</v>
+        <v>2.410117626190186</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4760,7 +4760,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D228">
-        <v>2.961266994476318</v>
+        <v>2.786337375640869</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4774,7 +4774,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D229">
-        <v>5.121443748474121</v>
+        <v>5.710762023925781</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="D230">
-        <v>1.364988207817078</v>
+        <v>1.356418013572693</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4802,7 +4802,7 @@
         <v>1</v>
       </c>
       <c r="D231">
-        <v>2.754698753356934</v>
+        <v>3.056948661804199</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4816,7 +4816,7 @@
         <v>25</v>
       </c>
       <c r="D232">
-        <v>14.52969932556152</v>
+        <v>18.46978569030762</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4830,7 +4830,7 @@
         <v>0.5</v>
       </c>
       <c r="D233">
-        <v>2.233076095581055</v>
+        <v>1.614702820777893</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4844,7 +4844,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D234">
-        <v>1.63250994682312</v>
+        <v>1.757572650909424</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4858,7 +4858,7 @@
         <v>17</v>
       </c>
       <c r="D235">
-        <v>16.21295356750488</v>
+        <v>16.72213935852051</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4872,7 +4872,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D236">
-        <v>5.669366836547852</v>
+        <v>6.264649391174316</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4886,7 +4886,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D237">
-        <v>2.640384912490845</v>
+        <v>2.728295564651489</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4900,7 +4900,7 @@
         <v>20.5</v>
       </c>
       <c r="D238">
-        <v>18.60906982421875</v>
+        <v>18.39156150817871</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4914,7 +4914,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D239">
-        <v>1.403653621673584</v>
+        <v>1.473626017570496</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4928,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="D240">
-        <v>1.397366046905518</v>
+        <v>1.288703203201294</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4942,7 +4942,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D241">
-        <v>2.008910179138184</v>
+        <v>1.928112864494324</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4956,7 +4956,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D242">
-        <v>3.062826633453369</v>
+        <v>3.738707780838013</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4970,7 +4970,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D243">
-        <v>1.395218133926392</v>
+        <v>1.383056402206421</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4984,7 +4984,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D244">
-        <v>1.589302539825439</v>
+        <v>1.747520208358765</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4998,7 +4998,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D245">
-        <v>1.38196873664856</v>
+        <v>1.53495454788208</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5012,7 +5012,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D246">
-        <v>3.073814392089844</v>
+        <v>3.37394380569458</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5026,7 +5026,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D247">
-        <v>4.074506759643555</v>
+        <v>3.86588454246521</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5040,7 +5040,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D248">
-        <v>2.54822564125061</v>
+        <v>2.642911434173584</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5054,7 +5054,7 @@
         <v>22.60000038146973</v>
       </c>
       <c r="D249">
-        <v>5.092321872711182</v>
+        <v>5.301776885986328</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5068,7 +5068,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D250">
-        <v>3.151116609573364</v>
+        <v>2.522083282470703</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5082,7 +5082,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D251">
-        <v>4.506045341491699</v>
+        <v>3.728098630905151</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5096,7 +5096,7 @@
         <v>3.5</v>
       </c>
       <c r="D252">
-        <v>1.726918816566467</v>
+        <v>4.072896957397461</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5110,7 +5110,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D253">
-        <v>1.415538787841797</v>
+        <v>2.937668323516846</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5124,7 +5124,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D254">
-        <v>2.590118169784546</v>
+        <v>4.251395225524902</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5138,7 +5138,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D255">
-        <v>5.510286331176758</v>
+        <v>5.893115997314453</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5152,7 +5152,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D256">
-        <v>1.406363964080811</v>
+        <v>1.901716709136963</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -5166,7 +5166,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D257">
-        <v>2.291922569274902</v>
+        <v>1.446968555450439</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -5180,7 +5180,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D258">
-        <v>2.542610168457031</v>
+        <v>2.426833868026733</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -5194,7 +5194,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D259">
-        <v>1.379187107086182</v>
+        <v>1.420726299285889</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -5208,7 +5208,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D260">
-        <v>2.557912349700928</v>
+        <v>3.354805946350098</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -5222,7 +5222,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D261">
-        <v>1.378251910209656</v>
+        <v>1.818670988082886</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -5236,7 +5236,7 @@
         <v>1</v>
       </c>
       <c r="D262">
-        <v>2.367028713226318</v>
+        <v>1.748983860015869</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -5250,7 +5250,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D263">
-        <v>3.152413845062256</v>
+        <v>4.424354553222656</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -5264,7 +5264,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D264">
-        <v>4.142602920532227</v>
+        <v>3.602294445037842</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -5278,7 +5278,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D265">
-        <v>2.510741949081421</v>
+        <v>1.606085777282715</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -5292,7 +5292,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D266">
-        <v>1.909187793731689</v>
+        <v>2.237728595733643</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5306,7 +5306,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D267">
-        <v>1.432276129722595</v>
+        <v>1.815455794334412</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5320,7 +5320,7 @@
         <v>37.20000076293945</v>
       </c>
       <c r="D268">
-        <v>24.38992118835449</v>
+        <v>22.03615760803223</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -5334,7 +5334,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D269">
-        <v>1.485440731048584</v>
+        <v>2.434927463531494</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -5348,7 +5348,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D270">
-        <v>2.320849418640137</v>
+        <v>2.208382129669189</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5362,7 +5362,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D271">
-        <v>4.179575443267822</v>
+        <v>3.634217023849487</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5376,7 +5376,7 @@
         <v>1.5</v>
       </c>
       <c r="D272">
-        <v>1.396109104156494</v>
+        <v>2.159307956695557</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5390,7 +5390,7 @@
         <v>0.5</v>
       </c>
       <c r="D273">
-        <v>1.668549776077271</v>
+        <v>1.911052942276001</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5404,7 +5404,7 @@
         <v>12.30000019073486</v>
       </c>
       <c r="D274">
-        <v>7.170547485351562</v>
+        <v>3.980040550231934</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5418,7 +5418,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D275">
-        <v>2.859447717666626</v>
+        <v>2.859498977661133</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5432,7 +5432,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D276">
-        <v>6.69289493560791</v>
+        <v>6.952528953552246</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5446,7 +5446,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D277">
-        <v>1.963278293609619</v>
+        <v>1.837320804595947</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5460,7 +5460,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D278">
-        <v>6.485502243041992</v>
+        <v>7.73326301574707</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5474,7 +5474,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D279">
-        <v>2.449088096618652</v>
+        <v>2.075423717498779</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5488,7 +5488,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D280">
-        <v>1.846701979637146</v>
+        <v>4.219597816467285</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5502,7 +5502,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D281">
-        <v>14.01164436340332</v>
+        <v>9.093222618103027</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5516,7 +5516,7 @@
         <v>15.60000038146973</v>
       </c>
       <c r="D282">
-        <v>9.00225830078125</v>
+        <v>9.154255867004395</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5530,7 +5530,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D283">
-        <v>1.370785117149353</v>
+        <v>1.38640570640564</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5544,7 +5544,7 @@
         <v>5</v>
       </c>
       <c r="D284">
-        <v>5.71776294708252</v>
+        <v>4.77464485168457</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5558,7 +5558,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D285">
-        <v>1.497462034225464</v>
+        <v>2.235008478164673</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5572,7 +5572,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D286">
-        <v>1.388934731483459</v>
+        <v>1.367560625076294</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5586,7 +5586,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D287">
-        <v>3.764731168746948</v>
+        <v>5.771081924438477</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5600,7 +5600,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D288">
-        <v>5.357935905456543</v>
+        <v>5.626042366027832</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5614,7 +5614,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D289">
-        <v>2.666627645492554</v>
+        <v>2.325599193572998</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5628,7 +5628,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D290">
-        <v>7.717277526855469</v>
+        <v>6.901190757751465</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5642,7 +5642,7 @@
         <v>2.5</v>
       </c>
       <c r="D291">
-        <v>2.006388664245605</v>
+        <v>2.838769674301147</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5656,7 +5656,7 @@
         <v>0</v>
       </c>
       <c r="D292">
-        <v>3.831954717636108</v>
+        <v>3.179494857788086</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5670,7 +5670,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D293">
-        <v>1.86256992816925</v>
+        <v>1.365808010101318</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5684,7 +5684,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D294">
-        <v>4.041775703430176</v>
+        <v>4.481626033782959</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5698,7 +5698,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D295">
-        <v>4.856223106384277</v>
+        <v>3.853222846984863</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5712,7 +5712,7 @@
         <v>6</v>
       </c>
       <c r="D296">
-        <v>2.615426540374756</v>
+        <v>1.915446043014526</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5726,7 +5726,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D297">
-        <v>2.999088287353516</v>
+        <v>3.634866952896118</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5740,7 +5740,7 @@
         <v>9.5</v>
       </c>
       <c r="D298">
-        <v>11.24261283874512</v>
+        <v>12.22553443908691</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5754,7 +5754,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D299">
-        <v>2.092677593231201</v>
+        <v>1.718747854232788</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5768,7 +5768,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D300">
-        <v>7.138283729553223</v>
+        <v>6.420011520385742</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5782,7 +5782,7 @@
         <v>9</v>
       </c>
       <c r="D301">
-        <v>2.899218082427979</v>
+        <v>3.716421365737915</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5796,7 +5796,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D302">
-        <v>2.038753032684326</v>
+        <v>4.302363872528076</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5810,7 +5810,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D303">
-        <v>1.920691609382629</v>
+        <v>1.816719770431519</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5824,7 +5824,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D304">
-        <v>1.464080214500427</v>
+        <v>1.921980977058411</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5838,7 +5838,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D305">
-        <v>2.336045980453491</v>
+        <v>2.310751438140869</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5852,7 +5852,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D306">
-        <v>1.778709173202515</v>
+        <v>1.758261919021606</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5866,7 +5866,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D307">
-        <v>4.858115196228027</v>
+        <v>5.466916084289551</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5880,7 +5880,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D308">
-        <v>1.390106797218323</v>
+        <v>1.838759779930115</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5894,7 +5894,7 @@
         <v>10.10000038146973</v>
       </c>
       <c r="D309">
-        <v>2.249146938323975</v>
+        <v>4.188107490539551</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5908,7 +5908,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D310">
-        <v>2.210056781768799</v>
+        <v>1.768325328826904</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5922,7 +5922,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D311">
-        <v>2.920412302017212</v>
+        <v>2.943377494812012</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5936,7 +5936,7 @@
         <v>2.5</v>
       </c>
       <c r="D312">
-        <v>1.703110933303833</v>
+        <v>1.953289151191711</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5950,7 +5950,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D313">
-        <v>1.398757815361023</v>
+        <v>1.489761352539062</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5964,7 +5964,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D314">
-        <v>2.559251070022583</v>
+        <v>2.360721349716187</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5978,7 +5978,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D315">
-        <v>1.638652563095093</v>
+        <v>1.545167684555054</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5992,7 +5992,7 @@
         <v>1</v>
       </c>
       <c r="D316">
-        <v>1.560063719749451</v>
+        <v>1.744175434112549</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -6006,7 +6006,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D317">
-        <v>1.371132493019104</v>
+        <v>1.307153701782227</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -6020,7 +6020,7 @@
         <v>8.5</v>
       </c>
       <c r="D318">
-        <v>3.21937894821167</v>
+        <v>2.642568111419678</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -6034,7 +6034,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D319">
-        <v>4.502979278564453</v>
+        <v>4.774264335632324</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -6048,7 +6048,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D320">
-        <v>6.833840370178223</v>
+        <v>8.002445220947266</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -6062,7 +6062,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D321">
-        <v>9.147295951843262</v>
+        <v>10.85756969451904</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -6076,7 +6076,7 @@
         <v>4</v>
       </c>
       <c r="D322">
-        <v>2.940474510192871</v>
+        <v>2.800073146820068</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -6090,7 +6090,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D323">
-        <v>2.677490711212158</v>
+        <v>2.030508279800415</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -6104,7 +6104,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D324">
-        <v>8.64128589630127</v>
+        <v>9.724635124206543</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -6118,7 +6118,7 @@
         <v>17.89999961853027</v>
       </c>
       <c r="D325">
-        <v>17.05874633789062</v>
+        <v>14.75198841094971</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -6132,7 +6132,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D326">
-        <v>4.449461936950684</v>
+        <v>3.59892463684082</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -6146,7 +6146,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D327">
-        <v>1.521771669387817</v>
+        <v>1.385494232177734</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6160,7 +6160,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D328">
-        <v>1.473164081573486</v>
+        <v>2.889626502990723</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -6174,7 +6174,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D329">
-        <v>1.498053669929504</v>
+        <v>1.864112973213196</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6188,7 +6188,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D330">
-        <v>2.491712093353271</v>
+        <v>2.231448650360107</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6202,7 +6202,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D331">
-        <v>1.403169631958008</v>
+        <v>1.376324057579041</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6216,7 +6216,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D332">
-        <v>1.665451407432556</v>
+        <v>1.708415150642395</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6230,7 +6230,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D333">
-        <v>2.506699323654175</v>
+        <v>1.676660060882568</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6244,7 +6244,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D334">
-        <v>2.469210386276245</v>
+        <v>1.934207558631897</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -6258,7 +6258,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D335">
-        <v>1.45690381526947</v>
+        <v>1.956964492797852</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -6272,7 +6272,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D336">
-        <v>2.338314771652222</v>
+        <v>1.953820109367371</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -6286,7 +6286,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D337">
-        <v>1.658849239349365</v>
+        <v>1.678078651428223</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6300,7 +6300,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D338">
-        <v>1.395432472229004</v>
+        <v>2.046358108520508</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6314,7 +6314,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D339">
-        <v>1.896019458770752</v>
+        <v>1.567493557929993</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6328,7 +6328,7 @@
         <v>23.20000076293945</v>
       </c>
       <c r="D340">
-        <v>10.9700756072998</v>
+        <v>11.90647983551025</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6342,7 +6342,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D341">
-        <v>2.188443183898926</v>
+        <v>2.173975706100464</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6356,7 +6356,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D342">
-        <v>2.915038108825684</v>
+        <v>3.023109912872314</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6370,7 +6370,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D343">
-        <v>1.819814443588257</v>
+        <v>1.578478217124939</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6384,7 +6384,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D344">
-        <v>2.468961477279663</v>
+        <v>2.719426393508911</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6398,7 +6398,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D345">
-        <v>2.964261531829834</v>
+        <v>2.514916181564331</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6412,7 +6412,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D346">
-        <v>6.48487663269043</v>
+        <v>6.748834609985352</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6426,7 +6426,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D347">
-        <v>4.948670387268066</v>
+        <v>4.819515228271484</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6440,7 +6440,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D348">
-        <v>4.017441749572754</v>
+        <v>4.472272872924805</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6454,7 +6454,7 @@
         <v>3</v>
       </c>
       <c r="D349">
-        <v>1.585912942886353</v>
+        <v>2.116189479827881</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6468,7 +6468,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D350">
-        <v>2.405707597732544</v>
+        <v>1.790579795837402</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6482,7 +6482,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D351">
-        <v>2.238845348358154</v>
+        <v>1.756633281707764</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6496,7 +6496,7 @@
         <v>0.5</v>
       </c>
       <c r="D352">
-        <v>1.37031078338623</v>
+        <v>1.414247989654541</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6510,7 +6510,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D353">
-        <v>2.521582126617432</v>
+        <v>2.779980182647705</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6524,7 +6524,7 @@
         <v>3.5</v>
       </c>
       <c r="D354">
-        <v>1.922406196594238</v>
+        <v>2.801887273788452</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6538,7 +6538,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D355">
-        <v>2.450719356536865</v>
+        <v>3.214849948883057</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6552,7 +6552,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D356">
-        <v>4.793849945068359</v>
+        <v>6.072689056396484</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6566,7 +6566,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D357">
-        <v>4.524514198303223</v>
+        <v>5.891408920288086</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6580,7 +6580,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D358">
-        <v>1.380016803741455</v>
+        <v>1.29533576965332</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6594,7 +6594,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D359">
-        <v>1.36596143245697</v>
+        <v>1.336468100547791</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6608,7 +6608,7 @@
         <v>1</v>
       </c>
       <c r="D360">
-        <v>1.457086205482483</v>
+        <v>2.281481742858887</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6622,7 +6622,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D361">
-        <v>2.010076522827148</v>
+        <v>2.178045988082886</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6636,7 +6636,7 @@
         <v>4.5</v>
       </c>
       <c r="D362">
-        <v>3.189685583114624</v>
+        <v>2.356451749801636</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6650,7 +6650,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D363">
-        <v>2.726179838180542</v>
+        <v>1.859109997749329</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6664,7 +6664,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D364">
-        <v>1.371858835220337</v>
+        <v>1.498322486877441</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6678,7 +6678,7 @@
         <v>35.09999847412109</v>
       </c>
       <c r="D365">
-        <v>25.80629730224609</v>
+        <v>28.2120189666748</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6692,7 +6692,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D366">
-        <v>2.41491174697876</v>
+        <v>1.781476974487305</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6706,7 +6706,7 @@
         <v>4</v>
       </c>
       <c r="D367">
-        <v>2.924108028411865</v>
+        <v>3.038712501525879</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6720,7 +6720,7 @@
         <v>2</v>
       </c>
       <c r="D368">
-        <v>1.385425567626953</v>
+        <v>1.565986275672913</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6734,7 +6734,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D369">
-        <v>4.102555274963379</v>
+        <v>3.918009757995605</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6748,7 +6748,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D370">
-        <v>1.827063322067261</v>
+        <v>2.756321907043457</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6762,7 +6762,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D371">
-        <v>2.357853889465332</v>
+        <v>3.213393449783325</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6776,7 +6776,7 @@
         <v>2.5</v>
       </c>
       <c r="D372">
-        <v>1.992776155471802</v>
+        <v>2.52592658996582</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6790,7 +6790,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D373">
-        <v>1.988674879074097</v>
+        <v>1.763018608093262</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6804,7 +6804,7 @@
         <v>1.5</v>
       </c>
       <c r="D374">
-        <v>5.367593765258789</v>
+        <v>4.087075233459473</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6818,7 +6818,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D375">
-        <v>5.873108863830566</v>
+        <v>4.71666431427002</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6832,7 +6832,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D376">
-        <v>6.007801055908203</v>
+        <v>5.299213409423828</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6846,7 +6846,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D377">
-        <v>4.730080604553223</v>
+        <v>6.02513313293457</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6860,7 +6860,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D378">
-        <v>1.393291831016541</v>
+        <v>1.6398766040802</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6874,7 +6874,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D379">
-        <v>1.705172181129456</v>
+        <v>1.440248370170593</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6888,7 +6888,7 @@
         <v>2.5</v>
       </c>
       <c r="D380">
-        <v>2.246773958206177</v>
+        <v>2.125782251358032</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6902,7 +6902,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D381">
-        <v>1.508863687515259</v>
+        <v>1.6402747631073</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6916,7 +6916,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D382">
-        <v>4.820382595062256</v>
+        <v>5.009181499481201</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6930,7 +6930,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D383">
-        <v>2.015107393264771</v>
+        <v>1.820758819580078</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6944,7 +6944,7 @@
         <v>12.69999980926514</v>
       </c>
       <c r="D384">
-        <v>2.011306047439575</v>
+        <v>2.633580207824707</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6958,7 +6958,7 @@
         <v>25.10000038146973</v>
       </c>
       <c r="D385">
-        <v>23.38475036621094</v>
+        <v>21.53800010681152</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -6972,7 +6972,7 @@
         <v>4.5</v>
       </c>
       <c r="D386">
-        <v>1.47710645198822</v>
+        <v>1.682920575141907</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -6986,7 +6986,7 @@
         <v>8</v>
       </c>
       <c r="D387">
-        <v>4.352033615112305</v>
+        <v>4.81513786315918</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -7000,7 +7000,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D388">
-        <v>2.435424089431763</v>
+        <v>2.170429229736328</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -7014,7 +7014,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D389">
-        <v>1.963822364807129</v>
+        <v>1.478587627410889</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -7028,7 +7028,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D390">
-        <v>1.741831302642822</v>
+        <v>1.972563743591309</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -7042,7 +7042,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D391">
-        <v>6.81611156463623</v>
+        <v>6.225955963134766</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -7056,7 +7056,7 @@
         <v>19</v>
       </c>
       <c r="D392">
-        <v>17.6153678894043</v>
+        <v>17.43806648254395</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -7070,7 +7070,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D393">
-        <v>2.546555519104004</v>
+        <v>2.375243663787842</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -7084,7 +7084,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D394">
-        <v>1.687885761260986</v>
+        <v>1.508668661117554</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -7098,7 +7098,7 @@
         <v>12</v>
       </c>
       <c r="D395">
-        <v>5.501111030578613</v>
+        <v>5.453900337219238</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -7112,7 +7112,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D396">
-        <v>2.639457225799561</v>
+        <v>3.253366947174072</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -7126,7 +7126,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D397">
-        <v>6.279019355773926</v>
+        <v>5.413786888122559</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -7140,7 +7140,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D398">
-        <v>7.214268684387207</v>
+        <v>8.030834197998047</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -7154,7 +7154,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D399">
-        <v>1.401117324829102</v>
+        <v>1.90664279460907</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7168,7 +7168,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D400">
-        <v>1.968138694763184</v>
+        <v>2.359222650527954</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7182,7 +7182,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D401">
-        <v>1.366769194602966</v>
+        <v>1.48259449005127</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -7196,7 +7196,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D402">
-        <v>5.610234260559082</v>
+        <v>6.154903411865234</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7210,7 +7210,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D403">
-        <v>2.120892524719238</v>
+        <v>1.94584858417511</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7224,7 +7224,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D404">
-        <v>4.70086669921875</v>
+        <v>4.329529762268066</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -7238,7 +7238,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D405">
-        <v>1.391915559768677</v>
+        <v>1.35122811794281</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7252,7 +7252,7 @@
         <v>3</v>
       </c>
       <c r="D406">
-        <v>1.96366810798645</v>
+        <v>2.047874450683594</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7266,7 +7266,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D407">
-        <v>2.479424715042114</v>
+        <v>2.028553009033203</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7280,7 +7280,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D408">
-        <v>2.431667327880859</v>
+        <v>2.469120025634766</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7294,7 +7294,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D409">
-        <v>9.300938606262207</v>
+        <v>9.491637229919434</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7308,7 +7308,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D410">
-        <v>1.385469436645508</v>
+        <v>1.353002071380615</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7322,7 +7322,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D411">
-        <v>1.607842803001404</v>
+        <v>1.649116992950439</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -7336,7 +7336,7 @@
         <v>1.5</v>
       </c>
       <c r="D412">
-        <v>1.735925078392029</v>
+        <v>1.654024958610535</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -7350,7 +7350,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D413">
-        <v>1.377268075942993</v>
+        <v>1.318570375442505</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7364,7 +7364,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D414">
-        <v>3.388632535934448</v>
+        <v>4.32692813873291</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7378,7 +7378,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D415">
-        <v>5.991298675537109</v>
+        <v>7.106522560119629</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7392,7 +7392,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D416">
-        <v>1.384328365325928</v>
+        <v>1.66990864276886</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7406,7 +7406,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D417">
-        <v>3.387356281280518</v>
+        <v>6.017130851745605</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7420,7 +7420,7 @@
         <v>5</v>
       </c>
       <c r="D418">
-        <v>2.024436950683594</v>
+        <v>2.008727550506592</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7434,7 +7434,7 @@
         <v>13</v>
       </c>
       <c r="D419">
-        <v>9.495647430419922</v>
+        <v>8.779098510742188</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7448,7 +7448,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D420">
-        <v>2.619165420532227</v>
+        <v>3.222733974456787</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7462,7 +7462,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D421">
-        <v>7.384183883666992</v>
+        <v>4.16878080368042</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7476,7 +7476,7 @@
         <v>22</v>
       </c>
       <c r="D422">
-        <v>15.72517967224121</v>
+        <v>15.12867450714111</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7490,7 +7490,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D423">
-        <v>1.421672105789185</v>
+        <v>1.342012882232666</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7504,7 +7504,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D424">
-        <v>1.593473553657532</v>
+        <v>1.883868932723999</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7518,7 +7518,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D425">
-        <v>9.144726753234863</v>
+        <v>6.162426948547363</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7532,7 +7532,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D426">
-        <v>3.087536811828613</v>
+        <v>3.843107938766479</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7546,7 +7546,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D427">
-        <v>1.388330698013306</v>
+        <v>1.289601922035217</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7560,7 +7560,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D428">
-        <v>1.447794437408447</v>
+        <v>1.911144733428955</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7574,7 +7574,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D429">
-        <v>5.74277400970459</v>
+        <v>5.95438289642334</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7588,7 +7588,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D430">
-        <v>4.273024559020996</v>
+        <v>4.302093029022217</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7602,7 +7602,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D431">
-        <v>6.805282592773438</v>
+        <v>8.085786819458008</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7616,7 +7616,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D432">
-        <v>1.37763237953186</v>
+        <v>1.351092219352722</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7630,7 +7630,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D433">
-        <v>2.973561525344849</v>
+        <v>2.733949422836304</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7644,7 +7644,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D434">
-        <v>1.39125919342041</v>
+        <v>1.815906882286072</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7658,7 +7658,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D435">
-        <v>2.626646995544434</v>
+        <v>2.386420011520386</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7672,7 +7672,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D436">
-        <v>2.462629079818726</v>
+        <v>2.135101318359375</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7686,7 +7686,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D437">
-        <v>1.366271734237671</v>
+        <v>1.664260149002075</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7700,7 +7700,7 @@
         <v>19.70000076293945</v>
       </c>
       <c r="D438">
-        <v>11.55111312866211</v>
+        <v>8.590229988098145</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7714,7 +7714,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D439">
-        <v>4.591933250427246</v>
+        <v>3.476044416427612</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7728,7 +7728,7 @@
         <v>0</v>
       </c>
       <c r="D440">
-        <v>1.712946176528931</v>
+        <v>1.527213096618652</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7742,7 +7742,7 @@
         <v>9</v>
       </c>
       <c r="D441">
-        <v>2.965975284576416</v>
+        <v>3.421656131744385</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7756,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="D442">
-        <v>1.416539430618286</v>
+        <v>2.078809261322021</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7770,7 +7770,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D443">
-        <v>1.787835955619812</v>
+        <v>1.910538196563721</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7784,7 +7784,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D444">
-        <v>2.129626512527466</v>
+        <v>2.216500043869019</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7798,7 +7798,7 @@
         <v>6</v>
       </c>
       <c r="D445">
-        <v>3.72932505607605</v>
+        <v>2.225461483001709</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7812,7 +7812,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D446">
-        <v>5.102232933044434</v>
+        <v>4.846482276916504</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7826,7 +7826,7 @@
         <v>3</v>
       </c>
       <c r="D447">
-        <v>1.774854302406311</v>
+        <v>2.011256694793701</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7840,7 +7840,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D448">
-        <v>2.030374050140381</v>
+        <v>1.685763716697693</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -7854,7 +7854,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D449">
-        <v>4.656453132629395</v>
+        <v>3.351278305053711</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -7868,7 +7868,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D450">
-        <v>2.136978149414062</v>
+        <v>2.838240385055542</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -7882,7 +7882,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D451">
-        <v>2.083991765975952</v>
+        <v>3.248073577880859</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -7896,7 +7896,7 @@
         <v>2</v>
       </c>
       <c r="D452">
-        <v>1.794631719589233</v>
+        <v>1.516420125961304</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -7910,7 +7910,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D453">
-        <v>3.917680501937866</v>
+        <v>7.094802856445312</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -7924,7 +7924,7 @@
         <v>0</v>
       </c>
       <c r="D454">
-        <v>1.375288486480713</v>
+        <v>2.086748123168945</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -7938,7 +7938,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D455">
-        <v>2.176325798034668</v>
+        <v>1.981588363647461</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -7952,7 +7952,7 @@
         <v>13</v>
       </c>
       <c r="D456">
-        <v>11.90225601196289</v>
+        <v>11.57183837890625</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -7966,7 +7966,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D457">
-        <v>3.337775945663452</v>
+        <v>3.56477952003479</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -7980,7 +7980,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D458">
-        <v>1.833072185516357</v>
+        <v>1.938112258911133</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -7994,7 +7994,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D459">
-        <v>2.226338624954224</v>
+        <v>3.994469165802002</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -8008,7 +8008,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D460">
-        <v>2.664009094238281</v>
+        <v>2.381694793701172</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -8022,7 +8022,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D461">
-        <v>2.964897632598877</v>
+        <v>2.782244443893433</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -8036,7 +8036,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D462">
-        <v>1.372578620910645</v>
+        <v>1.568890333175659</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -8050,7 +8050,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D463">
-        <v>1.391108274459839</v>
+        <v>1.392851591110229</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -8064,7 +8064,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D464">
-        <v>2.689637184143066</v>
+        <v>3.515958547592163</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -8078,7 +8078,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D465">
-        <v>3.725910902023315</v>
+        <v>4.469019412994385</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -8092,7 +8092,7 @@
         <v>0.5</v>
       </c>
       <c r="D466">
-        <v>2.356974124908447</v>
+        <v>1.83118212223053</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -8106,7 +8106,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D467">
-        <v>2.745945930480957</v>
+        <v>2.112684011459351</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -8120,7 +8120,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D468">
-        <v>1.77205228805542</v>
+        <v>1.654246926307678</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -8134,7 +8134,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D469">
-        <v>1.651266813278198</v>
+        <v>1.872791409492493</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -8148,7 +8148,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D470">
-        <v>3.884924650192261</v>
+        <v>4.047647476196289</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -8162,7 +8162,7 @@
         <v>3.5</v>
       </c>
       <c r="D471">
-        <v>1.426190853118896</v>
+        <v>1.964767456054688</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -8176,7 +8176,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D472">
-        <v>2.58636999130249</v>
+        <v>1.726192355155945</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -8190,7 +8190,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D473">
-        <v>1.374561071395874</v>
+        <v>1.425118684768677</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -8204,7 +8204,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D474">
-        <v>3.031424760818481</v>
+        <v>4.415126323699951</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -8218,7 +8218,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D475">
-        <v>6.375285148620605</v>
+        <v>6.521743774414062</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -8232,7 +8232,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D476">
-        <v>8.920317649841309</v>
+        <v>8.381580352783203</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -8246,7 +8246,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D477">
-        <v>2.10734224319458</v>
+        <v>1.780793070793152</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -8260,7 +8260,7 @@
         <v>2.5</v>
       </c>
       <c r="D478">
-        <v>2.664165496826172</v>
+        <v>2.953764200210571</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -8274,7 +8274,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D479">
-        <v>1.869639992713928</v>
+        <v>1.928126096725464</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -8288,7 +8288,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D480">
-        <v>2.282294750213623</v>
+        <v>2.319480895996094</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8302,7 +8302,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D481">
-        <v>1.447341084480286</v>
+        <v>1.745235919952393</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -8316,7 +8316,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D482">
-        <v>2.925750732421875</v>
+        <v>2.28612208366394</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -8330,7 +8330,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D483">
-        <v>1.382915496826172</v>
+        <v>1.662100195884705</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -8344,7 +8344,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D484">
-        <v>1.416274070739746</v>
+        <v>2.171174049377441</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8358,7 +8358,7 @@
         <v>36.09999847412109</v>
       </c>
       <c r="D485">
-        <v>20.74465179443359</v>
+        <v>18.67034339904785</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8372,7 +8372,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D486">
-        <v>1.392836689949036</v>
+        <v>1.644493579864502</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8386,7 +8386,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D487">
-        <v>3.288262605667114</v>
+        <v>4.529449462890625</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8400,7 +8400,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D488">
-        <v>1.710853576660156</v>
+        <v>1.920754075050354</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8414,7 +8414,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D489">
-        <v>2.323679447174072</v>
+        <v>3.339870691299438</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8428,7 +8428,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D490">
-        <v>3.544234991073608</v>
+        <v>4.586542129516602</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8442,7 +8442,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D491">
-        <v>2.535063505172729</v>
+        <v>2.486946582794189</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8456,7 +8456,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D492">
-        <v>5.317897796630859</v>
+        <v>5.117376327514648</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8470,7 +8470,7 @@
         <v>3</v>
       </c>
       <c r="D493">
-        <v>2.891098976135254</v>
+        <v>3.430822610855103</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -8484,7 +8484,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D494">
-        <v>1.919015645980835</v>
+        <v>1.674760818481445</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8498,7 +8498,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D495">
-        <v>2.681628704071045</v>
+        <v>2.756624221801758</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8512,7 +8512,7 @@
         <v>0.5</v>
       </c>
       <c r="D496">
-        <v>1.382390022277832</v>
+        <v>1.37573766708374</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8526,7 +8526,7 @@
         <v>2</v>
       </c>
       <c r="D497">
-        <v>2.188109636306763</v>
+        <v>2.419209480285645</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8540,7 +8540,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D498">
-        <v>1.408307552337646</v>
+        <v>1.971414566040039</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8554,7 +8554,7 @@
         <v>13</v>
       </c>
       <c r="D499">
-        <v>1.970345973968506</v>
+        <v>1.713412761688232</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8568,7 +8568,7 @@
         <v>7</v>
       </c>
       <c r="D500">
-        <v>2.907373428344727</v>
+        <v>3.0840744972229</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8582,7 +8582,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D501">
-        <v>2.164582252502441</v>
+        <v>1.452285766601562</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8596,7 +8596,7 @@
         <v>8.5</v>
       </c>
       <c r="D502">
-        <v>8.498510360717773</v>
+        <v>5.849814414978027</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -8610,7 +8610,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D503">
-        <v>2.664660453796387</v>
+        <v>3.338743448257446</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -8624,7 +8624,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D504">
-        <v>4.42512035369873</v>
+        <v>5.13493824005127</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -8638,7 +8638,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D505">
-        <v>2.775730609893799</v>
+        <v>2.20632529258728</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -8652,7 +8652,7 @@
         <v>6.5</v>
       </c>
       <c r="D506">
-        <v>2.130909442901611</v>
+        <v>3.618089437484741</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -8666,7 +8666,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D507">
-        <v>1.424970388412476</v>
+        <v>4.738007545471191</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -8680,7 +8680,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D508">
-        <v>2.878297090530396</v>
+        <v>1.666919827461243</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -8694,7 +8694,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D509">
-        <v>3.354202508926392</v>
+        <v>4.605634689331055</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -8708,7 +8708,7 @@
         <v>3</v>
       </c>
       <c r="D510">
-        <v>2.863447189331055</v>
+        <v>2.544384241104126</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -8722,7 +8722,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D511">
-        <v>3.328594207763672</v>
+        <v>3.238536596298218</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -8736,7 +8736,7 @@
         <v>32.5</v>
       </c>
       <c r="D512">
-        <v>20.43202018737793</v>
+        <v>17.47734642028809</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -8750,7 +8750,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D513">
-        <v>1.460405111312866</v>
+        <v>3.328273057937622</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -8764,7 +8764,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D514">
-        <v>2.161337852478027</v>
+        <v>2.821528196334839</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -8778,7 +8778,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D515">
-        <v>2.23384165763855</v>
+        <v>2.774097681045532</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -8792,7 +8792,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D516">
-        <v>1.462578535079956</v>
+        <v>1.866624355316162</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -8806,7 +8806,7 @@
         <v>1.5</v>
       </c>
       <c r="D517">
-        <v>1.386536598205566</v>
+        <v>1.316945791244507</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -8820,7 +8820,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D518">
-        <v>1.701308965682983</v>
+        <v>2.665785789489746</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -8834,7 +8834,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D519">
-        <v>6.508719444274902</v>
+        <v>4.462139129638672</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -8848,7 +8848,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D520">
-        <v>2.949486255645752</v>
+        <v>5.65385913848877</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -8862,7 +8862,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D521">
-        <v>10.56380844116211</v>
+        <v>10.46642780303955</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -8876,7 +8876,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D522">
-        <v>2.557487010955811</v>
+        <v>1.850502967834473</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -8890,7 +8890,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D523">
-        <v>7.506685256958008</v>
+        <v>9.1275634765625</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -8904,7 +8904,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D524">
-        <v>1.463696241378784</v>
+        <v>1.591759204864502</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -8918,7 +8918,7 @@
         <v>15.39999961853027</v>
       </c>
       <c r="D525">
-        <v>14.02147483825684</v>
+        <v>14.55186748504639</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -8932,7 +8932,7 @@
         <v>3</v>
       </c>
       <c r="D526">
-        <v>2.232679128646851</v>
+        <v>2.732575654983521</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -8946,7 +8946,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D527">
-        <v>5.432701110839844</v>
+        <v>5.936853408813477</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -8960,7 +8960,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D528">
-        <v>3.634701728820801</v>
+        <v>3.91399884223938</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -8974,7 +8974,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D529">
-        <v>2.170989036560059</v>
+        <v>2.481690168380737</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -8988,7 +8988,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D530">
-        <v>1.517743468284607</v>
+        <v>1.983273386955261</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9002,7 +9002,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D531">
-        <v>3.175740957260132</v>
+        <v>3.900389671325684</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -9016,7 +9016,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D532">
-        <v>1.386510133743286</v>
+        <v>1.343921661376953</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -9030,7 +9030,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D533">
-        <v>2.387841701507568</v>
+        <v>1.921189427375793</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -9044,7 +9044,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D534">
-        <v>2.392373085021973</v>
+        <v>1.435709953308105</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9058,7 +9058,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D535">
-        <v>6.015851974487305</v>
+        <v>6.749037742614746</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -9072,7 +9072,7 @@
         <v>26</v>
       </c>
       <c r="D536">
-        <v>15.63567352294922</v>
+        <v>15.34762001037598</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -9086,7 +9086,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D537">
-        <v>5.421945571899414</v>
+        <v>5.445202827453613</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -9100,7 +9100,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D538">
-        <v>2.556532859802246</v>
+        <v>1.711800456047058</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -9114,7 +9114,7 @@
         <v>15.89999961853027</v>
       </c>
       <c r="D539">
-        <v>9.802078247070312</v>
+        <v>11.20991706848145</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -9128,7 +9128,7 @@
         <v>27.5</v>
       </c>
       <c r="D540">
-        <v>12.04548358917236</v>
+        <v>9.079719543457031</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9142,7 +9142,7 @@
         <v>6</v>
       </c>
       <c r="D541">
-        <v>2.110590219497681</v>
+        <v>1.85917329788208</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -9156,7 +9156,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D542">
-        <v>4.643545150756836</v>
+        <v>4.882767677307129</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9170,7 +9170,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D543">
-        <v>1.995191097259521</v>
+        <v>1.845008611679077</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9184,7 +9184,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D544">
-        <v>1.705990314483643</v>
+        <v>1.879550933837891</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9198,7 +9198,7 @@
         <v>1.5</v>
       </c>
       <c r="D545">
-        <v>2.243935823440552</v>
+        <v>1.980847954750061</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -9212,7 +9212,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D546">
-        <v>2.068397760391235</v>
+        <v>2.023575305938721</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9226,7 +9226,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D547">
-        <v>7.763254165649414</v>
+        <v>8.266960144042969</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9240,7 +9240,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D548">
-        <v>3.010603904724121</v>
+        <v>3.549668550491333</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -9254,7 +9254,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D549">
-        <v>2.948262214660645</v>
+        <v>2.479187965393066</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9268,7 +9268,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D550">
-        <v>2.824322700500488</v>
+        <v>2.629474639892578</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9282,7 +9282,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D551">
-        <v>4.639601707458496</v>
+        <v>4.628388404846191</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -9296,7 +9296,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D552">
-        <v>6.020419120788574</v>
+        <v>6.558914184570312</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9310,7 +9310,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D553">
-        <v>1.979971051216125</v>
+        <v>2.071042776107788</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -9324,7 +9324,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D554">
-        <v>1.552552461624146</v>
+        <v>1.922805070877075</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -9338,7 +9338,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D555">
-        <v>1.366860151290894</v>
+        <v>1.310394525527954</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -9352,7 +9352,7 @@
         <v>2</v>
       </c>
       <c r="D556">
-        <v>2.110544681549072</v>
+        <v>2.183732986450195</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9366,7 +9366,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D557">
-        <v>2.0811927318573</v>
+        <v>2.204739570617676</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -9380,7 +9380,7 @@
         <v>6</v>
       </c>
       <c r="D558">
-        <v>4.137781143188477</v>
+        <v>4.861085891723633</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -9394,7 +9394,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D559">
-        <v>2.613413572311401</v>
+        <v>1.708874940872192</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -9408,7 +9408,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D560">
-        <v>2.23906135559082</v>
+        <v>1.892838597297668</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -9422,7 +9422,7 @@
         <v>4</v>
       </c>
       <c r="D561">
-        <v>2.54359769821167</v>
+        <v>2.459845066070557</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -9436,7 +9436,7 @@
         <v>2.5</v>
       </c>
       <c r="D562">
-        <v>2.742086887359619</v>
+        <v>2.807318687438965</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -9450,7 +9450,7 @@
         <v>1.5</v>
       </c>
       <c r="D563">
-        <v>2.620069026947021</v>
+        <v>3.180685758590698</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -9464,7 +9464,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D564">
-        <v>1.890751242637634</v>
+        <v>2.469482660293579</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -9478,7 +9478,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D565">
-        <v>1.635037541389465</v>
+        <v>1.72453761100769</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -9492,7 +9492,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D566">
-        <v>2.630165338516235</v>
+        <v>2.205933809280396</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -9506,7 +9506,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D567">
-        <v>6.04207706451416</v>
+        <v>6.276103019714355</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -9520,7 +9520,7 @@
         <v>5.5</v>
       </c>
       <c r="D568">
-        <v>4.582123756408691</v>
+        <v>5.132987022399902</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -9534,7 +9534,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D569">
-        <v>4.776612281799316</v>
+        <v>5.002383232116699</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -9548,7 +9548,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D570">
-        <v>2.570427656173706</v>
+        <v>1.458179116249084</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -9562,7 +9562,7 @@
         <v>4</v>
       </c>
       <c r="D571">
-        <v>1.462640881538391</v>
+        <v>1.658599138259888</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -9576,7 +9576,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D572">
-        <v>1.400961399078369</v>
+        <v>1.595859050750732</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -9590,7 +9590,7 @@
         <v>1.5</v>
       </c>
       <c r="D573">
-        <v>4.2489013671875</v>
+        <v>5.124320030212402</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -9604,7 +9604,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D574">
-        <v>3.776736497879028</v>
+        <v>4.393195152282715</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -9618,7 +9618,7 @@
         <v>0</v>
       </c>
       <c r="D575">
-        <v>1.588925004005432</v>
+        <v>1.582818508148193</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -9632,7 +9632,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D576">
-        <v>3.57787013053894</v>
+        <v>4.044582366943359</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -9646,7 +9646,7 @@
         <v>0.5</v>
       </c>
       <c r="D577">
-        <v>1.408153653144836</v>
+        <v>1.413598656654358</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -9660,7 +9660,7 @@
         <v>0.5</v>
       </c>
       <c r="D578">
-        <v>2.876431465148926</v>
+        <v>4.498453140258789</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -9674,7 +9674,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>3.547564029693604</v>
+        <v>5.081342697143555</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -9688,7 +9688,7 @@
         <v>16.10000038146973</v>
       </c>
       <c r="D580">
-        <v>17.28123664855957</v>
+        <v>20.04148292541504</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -9702,7 +9702,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D581">
-        <v>2.697169303894043</v>
+        <v>1.835276246070862</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -9716,7 +9716,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D582">
-        <v>1.450069665908813</v>
+        <v>1.562685251235962</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -9730,7 +9730,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D583">
-        <v>2.653164386749268</v>
+        <v>2.564377784729004</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -9744,7 +9744,7 @@
         <v>0</v>
       </c>
       <c r="D584">
-        <v>2.420292377471924</v>
+        <v>2.774338483810425</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -9758,7 +9758,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D585">
-        <v>1.770376324653625</v>
+        <v>1.997606873512268</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -9772,7 +9772,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D586">
-        <v>5.756091117858887</v>
+        <v>4.997313022613525</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -9786,7 +9786,7 @@
         <v>2</v>
       </c>
       <c r="D587">
-        <v>1.974446296691895</v>
+        <v>3.445873022079468</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -9800,7 +9800,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D588">
-        <v>2.608104944229126</v>
+        <v>1.928060531616211</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -9814,7 +9814,7 @@
         <v>10</v>
       </c>
       <c r="D589">
-        <v>4.625423908233643</v>
+        <v>5.363397598266602</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -9828,7 +9828,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D590">
-        <v>1.399424910545349</v>
+        <v>1.986051082611084</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -9842,7 +9842,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D591">
-        <v>1.794443130493164</v>
+        <v>1.773422479629517</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -9856,7 +9856,7 @@
         <v>34.59999847412109</v>
       </c>
       <c r="D592">
-        <v>32.48505401611328</v>
+        <v>35.34201812744141</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -9870,7 +9870,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D593">
-        <v>5.482571601867676</v>
+        <v>6.177769660949707</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -9884,7 +9884,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D594">
-        <v>2.376347303390503</v>
+        <v>2.862873554229736</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -9898,7 +9898,7 @@
         <v>0.5</v>
       </c>
       <c r="D595">
-        <v>1.378239512443542</v>
+        <v>1.543931484222412</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -9912,7 +9912,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D596">
-        <v>3.300864934921265</v>
+        <v>2.661217927932739</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -9926,7 +9926,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D597">
-        <v>2.000822305679321</v>
+        <v>1.662042379379272</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -9940,7 +9940,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D598">
-        <v>3.851735353469849</v>
+        <v>3.396274328231812</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -9954,7 +9954,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D599">
-        <v>4.705988883972168</v>
+        <v>4.56534481048584</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -9968,7 +9968,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D600">
-        <v>2.967188835144043</v>
+        <v>2.574389219284058</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -9982,7 +9982,7 @@
         <v>12.19999980926514</v>
       </c>
       <c r="D601">
-        <v>6.743072509765625</v>
+        <v>7.031566619873047</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -9996,7 +9996,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D602">
-        <v>1.428550720214844</v>
+        <v>1.839628338813782</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -10010,7 +10010,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D603">
-        <v>1.396822810173035</v>
+        <v>1.649991750717163</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -10024,7 +10024,7 @@
         <v>1</v>
       </c>
       <c r="D604">
-        <v>1.403852462768555</v>
+        <v>2.231757640838623</v>
       </c>
     </row>
     <row r="605" spans="1:4">
@@ -10038,7 +10038,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D605">
-        <v>4.876383781433105</v>
+        <v>5.021333694458008</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -10052,7 +10052,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D606">
-        <v>1.383542537689209</v>
+        <v>1.283977031707764</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -10066,7 +10066,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D607">
-        <v>2.322109699249268</v>
+        <v>1.640210866928101</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -10080,7 +10080,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D608">
-        <v>5.160027503967285</v>
+        <v>4.46823787689209</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -10094,7 +10094,7 @@
         <v>0.5</v>
       </c>
       <c r="D609">
-        <v>2.226871013641357</v>
+        <v>1.742528557777405</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -10108,7 +10108,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D610">
-        <v>2.018060684204102</v>
+        <v>2.114464521408081</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -10122,7 +10122,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D611">
-        <v>3.527464628219604</v>
+        <v>2.920286655426025</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -10136,7 +10136,7 @@
         <v>3</v>
       </c>
       <c r="D612">
-        <v>1.559867262840271</v>
+        <v>3.078455448150635</v>
       </c>
     </row>
   </sheetData>
